--- a/재정학/재정학 그래프.xlsx
+++ b/재정학/재정학 그래프.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DESKTOP\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DESKTOP\Desktop\Teaching\재정학\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7454D535-711A-43FD-AF3C-C09BC9CBD833}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43FE0EFA-BC82-4E3B-91F8-C5BFCF62767F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="57480" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{96D50BE9-6D5F-4E3E-9BD3-4B70E497608C}"/>
   </bookViews>
@@ -37,17 +37,13 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="63">
   <si>
     <t>기능별 분류</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>성질별 분류</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>이건비</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -144,6 +140,189 @@
   </si>
   <si>
     <t>43p 그림2-3</t>
+  </si>
+  <si>
+    <t>사진으로 대체</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>49p 그림2-4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>인건비</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>일반회계</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>특별회계</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>기금</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>재정수입</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>재정지출</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>일반공공행정</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>문화 및 관광</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>환경</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>보건</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>과학기술</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>예비비</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>인력운영비</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>기본경비등</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>농림 해양 수산</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>산업</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>중소기업 및 에너지</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>국토 및 지역개발</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>51p 그림 2-6</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>52p 그림 2-7</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1990년</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1995년</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2000년</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2005년</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2010년</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2015년</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2019년</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>중앙정부</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>지방정부</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>조세수입</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>54p 그림 2-8</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>취득세</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>지방소비세</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>지방소득세</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>재산세</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>자동차세</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>지방교육세</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>담배소비세</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>주민세</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -2171,6 +2350,2876 @@
 </c:chartSpace>
 </file>
 
+<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="ko-KR"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:autoTitleDeleted val="1"/>
+    <c:plotArea>
+      <c:layout>
+        <c:manualLayout>
+          <c:layoutTarget val="inner"/>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="0.17081692913385826"/>
+          <c:y val="1.7161718048956682E-2"/>
+          <c:w val="0.80087658291178487"/>
+          <c:h val="0.98283828195104328"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:barChart>
+        <c:barDir val="bar"/>
+        <c:grouping val="percentStacked"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="bg1"/>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="ko-KR"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="ctr"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sheet1!$B$43:$B$44</c:f>
+              <c:strCache>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>재정지출</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>재정수입</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$C$43:$C$44</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>77.900000000000006</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>88.9</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-A29F-46C8-895C-EB747543278A}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent2"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="bg1"/>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="ko-KR"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="ctr"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sheet1!$B$43:$B$44</c:f>
+              <c:strCache>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>재정지출</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>재정수입</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$D$43:$D$44</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>10</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-A29F-46C8-895C-EB747543278A}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent3"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="bg1"/>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="ko-KR"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="ctr"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sheet1!$B$43:$B$44</c:f>
+              <c:strCache>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>재정지출</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>재정수입</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$E$43:$E$44</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000003-A29F-46C8-895C-EB747543278A}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:dLblPos val="ctr"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="150"/>
+        <c:overlap val="100"/>
+        <c:axId val="1100748287"/>
+        <c:axId val="1100731967"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="1100748287"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ko-KR"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1100731967"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1100731967"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="1"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="0%" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="1100748287"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln w="25400">
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="ko-KR"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="ko-KR"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:autoTitleDeleted val="1"/>
+    <c:plotArea>
+      <c:layout>
+        <c:manualLayout>
+          <c:layoutTarget val="inner"/>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="6.6331625386743504E-2"/>
+          <c:y val="5.1044083526682132E-2"/>
+          <c:w val="0.83640359923824492"/>
+          <c:h val="0.47200358075890164"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="ko-KR"/>
+              </a:p>
+            </c:txPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sheet1!$B$49:$B$63</c:f>
+              <c:strCache>
+                <c:ptCount val="15"/>
+                <c:pt idx="0">
+                  <c:v>일반공공행정</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>공공질서 및 안전</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>교육</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>문화 및 관광</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>환경</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>사회복지</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>보건</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>농림 해양 수산</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>산업·중소기업 및 에너지</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>교통 및 물류</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>국토 및 지역개발</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>과학기술</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>예비비</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>인력운영비</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>기본경비등</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$C$49:$C$63</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="15"/>
+                <c:pt idx="0">
+                  <c:v>4.9000000000000004</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1.6</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>5.5</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>4.8</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>10.1</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>29.8</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>1.6</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>6.4</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>7.7</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>6.9</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.1</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>1.8</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>12.5</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>3.2</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-96AA-4BF3-954E-99F201FF6B01}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="219"/>
+        <c:overlap val="-27"/>
+        <c:axId val="1679617199"/>
+        <c:axId val="1679609999"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="1679617199"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="eaVert" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="700" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ko-KR"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1679609999"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1679609999"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ko-KR"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1679617199"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="ko-KR"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="ko-KR"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:autoTitleDeleted val="1"/>
+    <c:plotArea>
+      <c:layout>
+        <c:manualLayout>
+          <c:layoutTarget val="inner"/>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="0.11696560183106458"/>
+          <c:y val="5.0925925925925923E-2"/>
+          <c:w val="0.83340991972665446"/>
+          <c:h val="0.76854913969087202"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:barChart>
+        <c:barDir val="bar"/>
+        <c:grouping val="stacked"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$C$66</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>중앙정부</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="bg1"/>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="ko-KR"/>
+              </a:p>
+            </c:txPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sheet1!$B$67:$B$73</c:f>
+              <c:strCache>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>2019년</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2015년</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2010년</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2005년</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2000년</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1995년</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>1990년</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$C$67:$C$73</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>59</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>58.5</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>60.3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>57.8</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>61.6</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>58.4</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>63.9</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-63D7-49FC-8029-8167803BC07D}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$D$66</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>지방정부</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent2"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="bg1"/>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="ko-KR"/>
+              </a:p>
+            </c:txPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sheet1!$B$67:$B$73</c:f>
+              <c:strCache>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>2019년</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2015년</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2010년</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2005년</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2000년</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1995년</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>1990년</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$D$67:$D$73</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>41</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>41.5</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>39.700000000000003</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>42.2</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>38.4</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>41.6</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>36.1</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-63D7-49FC-8029-8167803BC07D}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="150"/>
+        <c:overlap val="100"/>
+        <c:axId val="1679663279"/>
+        <c:axId val="1679664239"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="1679663279"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ko-KR"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1679664239"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1679664239"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:max val="100"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ko-KR"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1679663279"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="ko-KR"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="ko-KR"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart7.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="ko-KR"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:autoTitleDeleted val="1"/>
+    <c:plotArea>
+      <c:layout>
+        <c:manualLayout>
+          <c:layoutTarget val="inner"/>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="0.11696560183106458"/>
+          <c:y val="5.0925925925925923E-2"/>
+          <c:w val="0.83340991972665446"/>
+          <c:h val="0.76854913969087202"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:barChart>
+        <c:barDir val="bar"/>
+        <c:grouping val="stacked"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$C$66</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>중앙정부</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="bg1"/>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="ko-KR"/>
+              </a:p>
+            </c:txPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sheet1!$B$78:$B$84</c:f>
+              <c:strCache>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>2019년</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2015년</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2010년</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2005년</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2000년</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1995년</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>1990년</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$C$78:$C$84</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>77.5</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>75.400000000000006</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>78.3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>78</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>81.900000000000006</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>78.8</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>80.8</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-63D7-49FC-8029-8167803BC07D}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$D$66</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>지방정부</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent2"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="bg1"/>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="ko-KR"/>
+              </a:p>
+            </c:txPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sheet1!$B$78:$B$84</c:f>
+              <c:strCache>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>2019년</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2015년</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2010년</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2005년</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2000년</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1995년</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>1990년</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$D$78:$D$84</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>22.5</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>24.6</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>21.7</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>22</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>18.100000000000001</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>21.2</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>19.2</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-63D7-49FC-8029-8167803BC07D}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="150"/>
+        <c:overlap val="100"/>
+        <c:axId val="1679663279"/>
+        <c:axId val="1679664239"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="1679663279"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ko-KR"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1679664239"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1679664239"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:max val="100"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ko-KR"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1679663279"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="ko-KR"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="ko-KR"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart8.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="ko-KR"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:autoTitleDeleted val="1"/>
+    <c:plotArea>
+      <c:layout>
+        <c:manualLayout>
+          <c:layoutTarget val="inner"/>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="2.2591899410205419E-3"/>
+          <c:y val="9.8434073831896868E-2"/>
+          <c:w val="0.99348932941675916"/>
+          <c:h val="0.90156625935966905"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:barChart>
+        <c:barDir val="bar"/>
+        <c:grouping val="percentStacked"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="bg1"/>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="ko-KR"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="ctr"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:numRef>
+              <c:f>Sheet1!$B$101</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="1"/>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$C$101</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>24.5</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-DC1B-4E16-9208-857F3844E14C}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent2"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="bg1"/>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="ko-KR"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="ctr"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:numRef>
+              <c:f>Sheet1!$B$101</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="1"/>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$D$101</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>17.7</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-DC1B-4E16-9208-857F3844E14C}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent3"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="bg1"/>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="ko-KR"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="ctr"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:numRef>
+              <c:f>Sheet1!$B$101</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="1"/>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$E$101</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>16.600000000000001</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-DC1B-4E16-9208-857F3844E14C}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="3"/>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent4"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="bg1"/>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="ko-KR"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="ctr"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:numRef>
+              <c:f>Sheet1!$B$101</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="1"/>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$F$101</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>14.1</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000003-DC1B-4E16-9208-857F3844E14C}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="4"/>
+          <c:order val="4"/>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent5"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="bg1"/>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="ko-KR"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="ctr"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:numRef>
+              <c:f>Sheet1!$B$101</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="1"/>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$G$101</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>8.4</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000004-DC1B-4E16-9208-857F3844E14C}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="5"/>
+          <c:order val="5"/>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent6"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="bg1"/>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="ko-KR"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="ctr"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:numRef>
+              <c:f>Sheet1!$B$101</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="1"/>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$H$101</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>7.2</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000005-DC1B-4E16-9208-857F3844E14C}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="6"/>
+          <c:order val="6"/>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1">
+                <a:lumMod val="60000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="700" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="bg1"/>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="ko-KR"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="ctr"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:numRef>
+              <c:f>Sheet1!$B$101</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="1"/>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$I$101</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>3.6</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000008-DC1B-4E16-9208-857F3844E14C}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="7"/>
+          <c:order val="7"/>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent2">
+                <a:lumMod val="60000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="700" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="bg1"/>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="ko-KR"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="ctr"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:numRef>
+              <c:f>Sheet1!$B$101</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="1"/>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$J$101</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>2.2999999999999998</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000009-DC1B-4E16-9208-857F3844E14C}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="8"/>
+          <c:order val="8"/>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent3">
+                <a:lumMod val="60000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="700" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="bg1"/>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="ko-KR"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="ctr"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:numRef>
+              <c:f>Sheet1!$B$101</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="1"/>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$K$101</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>5.7</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{0000000A-DC1B-4E16-9208-857F3844E14C}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:dLblPos val="ctr"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="150"/>
+        <c:overlap val="100"/>
+        <c:axId val="1100748287"/>
+        <c:axId val="1100731967"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="1100748287"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="1"/>
+        <c:axPos val="l"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="1100731967"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1100731967"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="1"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="0%" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="1100748287"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln w="25400">
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="ko-KR"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
 <file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
@@ -2291,6 +5340,206 @@
 </cs:colorStyle>
 </file>
 
+<file path=xl/charts/colors4.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors5.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors6.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors7.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors8.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
 <file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="297">
   <cs:axisTitle>
@@ -3303,6 +6552,2529 @@
 
 <file path=xl/charts/style3.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="216">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style4.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="297">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style5.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style6.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="297">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style7.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="297">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style8.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="297">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
@@ -3911,6 +9683,190 @@
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
           <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>619262</xdr:colOff>
+      <xdr:row>36</xdr:row>
+      <xdr:rowOff>35062</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>288096</xdr:colOff>
+      <xdr:row>42</xdr:row>
+      <xdr:rowOff>149361</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="7" name="차트 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4499617B-1188-6FA0-29B6-A302DD0EFA65}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>180009</xdr:colOff>
+      <xdr:row>45</xdr:row>
+      <xdr:rowOff>28161</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>545686</xdr:colOff>
+      <xdr:row>57</xdr:row>
+      <xdr:rowOff>180837</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="8" name="차트 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{16105777-1451-8EC7-8417-24C443C60E9D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId5"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>207065</xdr:colOff>
+      <xdr:row>60</xdr:row>
+      <xdr:rowOff>2070</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>556868</xdr:colOff>
+      <xdr:row>72</xdr:row>
+      <xdr:rowOff>161097</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="9" name="차트 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C8D18DBE-D747-1200-8168-4998B7C2CE19}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId6"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>198783</xdr:colOff>
+      <xdr:row>74</xdr:row>
+      <xdr:rowOff>78547</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>558111</xdr:colOff>
+      <xdr:row>87</xdr:row>
+      <xdr:rowOff>31750</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="10" name="차트 9">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{248E6EA8-EA9A-55A0-7074-4C98C655D3E1}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId7"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>405848</xdr:colOff>
+      <xdr:row>102</xdr:row>
+      <xdr:rowOff>8284</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>84207</xdr:colOff>
+      <xdr:row>108</xdr:row>
+      <xdr:rowOff>109331</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="11" name="차트 10">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{54BBD3DA-0363-452F-8606-B768A56A8B09}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId8"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -4236,10 +10192,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A956BE86-58C2-41A9-BF2A-798A8FD362D8}">
-  <dimension ref="B4:I37"/>
+  <dimension ref="A4:K101"/>
   <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="2" max="2" width="11.58203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="13.5" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="16.5" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="12.33203125" bestFit="1" customWidth="1"/>
@@ -4247,25 +10203,25 @@
   <sheetData>
     <row r="4" spans="2:9" x14ac:dyDescent="0.45">
       <c r="C4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D4" t="s">
         <v>8</v>
       </c>
-      <c r="D4" t="s">
+      <c r="E4" t="s">
         <v>9</v>
       </c>
-      <c r="E4" t="s">
+      <c r="F4" t="s">
         <v>10</v>
       </c>
-      <c r="F4" t="s">
+      <c r="G4" t="s">
         <v>11</v>
       </c>
-      <c r="G4" t="s">
+      <c r="H4" t="s">
         <v>12</v>
       </c>
-      <c r="H4" t="s">
-        <v>13</v>
-      </c>
       <c r="I4" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5" spans="2:9" x14ac:dyDescent="0.45">
@@ -4296,22 +10252,22 @@
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.45">
       <c r="C9" t="s">
+        <v>25</v>
+      </c>
+      <c r="D9" t="s">
         <v>2</v>
       </c>
-      <c r="D9" t="s">
+      <c r="E9" t="s">
         <v>3</v>
       </c>
-      <c r="E9" t="s">
+      <c r="F9" t="s">
         <v>4</v>
       </c>
-      <c r="F9" t="s">
+      <c r="G9" t="s">
         <v>5</v>
       </c>
-      <c r="G9" t="s">
+      <c r="H9" t="s">
         <v>6</v>
-      </c>
-      <c r="H9" t="s">
-        <v>7</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.45">
@@ -4339,13 +10295,13 @@
     </row>
     <row r="24" spans="3:7" x14ac:dyDescent="0.45">
       <c r="C24" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D24">
         <v>46.97</v>
       </c>
       <c r="F24" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G24">
         <v>16.440000000000001</v>
@@ -4353,13 +10309,13 @@
     </row>
     <row r="25" spans="3:7" x14ac:dyDescent="0.45">
       <c r="C25" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D25">
         <v>42.54</v>
       </c>
       <c r="F25" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G25">
         <v>22.37</v>
@@ -4367,13 +10323,13 @@
     </row>
     <row r="26" spans="3:7" x14ac:dyDescent="0.45">
       <c r="C26" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D26">
         <v>39.21</v>
       </c>
       <c r="F26" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G26">
         <v>24.98</v>
@@ -4381,13 +10337,13 @@
     </row>
     <row r="27" spans="3:7" x14ac:dyDescent="0.45">
       <c r="C27" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D27">
         <v>36.950000000000003</v>
       </c>
       <c r="F27" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G27">
         <v>28.07</v>
@@ -4395,13 +10351,13 @@
     </row>
     <row r="28" spans="3:7" x14ac:dyDescent="0.45">
       <c r="C28" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D28">
         <v>31.74</v>
       </c>
       <c r="F28" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G28">
         <v>31.74</v>
@@ -4409,13 +10365,13 @@
     </row>
     <row r="29" spans="3:7" x14ac:dyDescent="0.45">
       <c r="C29" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D29">
         <v>28.07</v>
       </c>
       <c r="F29" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G29">
         <v>36.950000000000003</v>
@@ -4423,13 +10379,13 @@
     </row>
     <row r="30" spans="3:7" x14ac:dyDescent="0.45">
       <c r="C30" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D30">
         <v>24.98</v>
       </c>
       <c r="F30" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G30">
         <v>39.21</v>
@@ -4437,13 +10393,13 @@
     </row>
     <row r="31" spans="3:7" x14ac:dyDescent="0.45">
       <c r="C31" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D31">
         <v>22.37</v>
       </c>
       <c r="F31" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G31">
         <v>42.54</v>
@@ -4451,21 +10407,511 @@
     </row>
     <row r="32" spans="3:7" x14ac:dyDescent="0.45">
       <c r="C32" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D32">
         <v>16.440000000000001</v>
       </c>
       <c r="F32" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G32">
         <v>46.97</v>
       </c>
     </row>
-    <row r="37" spans="2:2" x14ac:dyDescent="0.45">
-      <c r="B37" t="s">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A37" t="s">
+        <v>22</v>
+      </c>
+      <c r="C37" t="s">
         <v>23</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A40" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="C42" t="s">
+        <v>26</v>
+      </c>
+      <c r="D42" t="s">
+        <v>27</v>
+      </c>
+      <c r="E42" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="B43" t="s">
+        <v>30</v>
+      </c>
+      <c r="C43">
+        <v>77.900000000000006</v>
+      </c>
+      <c r="D43">
+        <v>20</v>
+      </c>
+      <c r="E43">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="B44" t="s">
+        <v>29</v>
+      </c>
+      <c r="C44">
+        <v>88.9</v>
+      </c>
+      <c r="D44">
+        <v>10</v>
+      </c>
+      <c r="E44">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A48" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="49" spans="2:3" x14ac:dyDescent="0.45">
+      <c r="B49" t="s">
+        <v>31</v>
+      </c>
+      <c r="C49">
+        <v>4.9000000000000004</v>
+      </c>
+    </row>
+    <row r="50" spans="2:3" x14ac:dyDescent="0.45">
+      <c r="B50" t="s">
+        <v>8</v>
+      </c>
+      <c r="C50">
+        <v>1.6</v>
+      </c>
+    </row>
+    <row r="51" spans="2:3" x14ac:dyDescent="0.45">
+      <c r="B51" t="s">
+        <v>10</v>
+      </c>
+      <c r="C51">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="52" spans="2:3" x14ac:dyDescent="0.45">
+      <c r="B52" t="s">
+        <v>32</v>
+      </c>
+      <c r="C52">
+        <v>4.8</v>
+      </c>
+    </row>
+    <row r="53" spans="2:3" x14ac:dyDescent="0.45">
+      <c r="B53" t="s">
+        <v>33</v>
+      </c>
+      <c r="C53">
+        <v>10.1</v>
+      </c>
+    </row>
+    <row r="54" spans="2:3" x14ac:dyDescent="0.45">
+      <c r="B54" t="s">
+        <v>11</v>
+      </c>
+      <c r="C54">
+        <v>29.8</v>
+      </c>
+    </row>
+    <row r="55" spans="2:3" x14ac:dyDescent="0.45">
+      <c r="B55" t="s">
+        <v>34</v>
+      </c>
+      <c r="C55">
+        <v>1.6</v>
+      </c>
+    </row>
+    <row r="56" spans="2:3" x14ac:dyDescent="0.45">
+      <c r="B56" t="s">
+        <v>39</v>
+      </c>
+      <c r="C56">
+        <v>6.4</v>
+      </c>
+    </row>
+    <row r="57" spans="2:3" x14ac:dyDescent="0.45">
+      <c r="B57" t="s">
+        <v>40</v>
+      </c>
+      <c r="C57">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="2:3" x14ac:dyDescent="0.45">
+      <c r="B58" t="s">
+        <v>12</v>
+      </c>
+      <c r="C58">
+        <v>7.7</v>
+      </c>
+    </row>
+    <row r="59" spans="2:3" x14ac:dyDescent="0.45">
+      <c r="B59" t="s">
+        <v>41</v>
+      </c>
+      <c r="C59">
+        <v>6.9</v>
+      </c>
+    </row>
+    <row r="60" spans="2:3" x14ac:dyDescent="0.45">
+      <c r="B60" t="s">
+        <v>35</v>
+      </c>
+      <c r="C60">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="61" spans="2:3" x14ac:dyDescent="0.45">
+      <c r="B61" t="s">
+        <v>36</v>
+      </c>
+      <c r="C61">
+        <v>1.8</v>
+      </c>
+    </row>
+    <row r="62" spans="2:3" x14ac:dyDescent="0.45">
+      <c r="B62" t="s">
+        <v>37</v>
+      </c>
+      <c r="C62">
+        <v>12.5</v>
+      </c>
+    </row>
+    <row r="63" spans="2:3" x14ac:dyDescent="0.45">
+      <c r="B63" t="s">
+        <v>38</v>
+      </c>
+      <c r="C63">
+        <v>3.2</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A65" t="s">
+        <v>43</v>
+      </c>
+      <c r="C65" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="C66" t="s">
+        <v>51</v>
+      </c>
+      <c r="D66" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="B67" t="s">
+        <v>50</v>
+      </c>
+      <c r="C67">
+        <v>59</v>
+      </c>
+      <c r="D67">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="B68" t="s">
+        <v>49</v>
+      </c>
+      <c r="C68">
+        <v>58.5</v>
+      </c>
+      <c r="D68">
+        <v>41.5</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="B69" t="s">
+        <v>48</v>
+      </c>
+      <c r="C69">
+        <v>60.3</v>
+      </c>
+      <c r="D69">
+        <v>39.700000000000003</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="B70" t="s">
+        <v>47</v>
+      </c>
+      <c r="C70">
+        <v>57.8</v>
+      </c>
+      <c r="D70">
+        <v>42.2</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="B71" t="s">
+        <v>46</v>
+      </c>
+      <c r="C71">
+        <v>61.6</v>
+      </c>
+      <c r="D71">
+        <v>38.4</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="B72" t="s">
+        <v>45</v>
+      </c>
+      <c r="C72">
+        <v>58.4</v>
+      </c>
+      <c r="D72">
+        <v>41.6</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="B73" t="s">
+        <v>44</v>
+      </c>
+      <c r="C73">
+        <v>63.9</v>
+      </c>
+      <c r="D73">
+        <v>36.1</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="C76" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="77" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="C77" t="s">
+        <v>51</v>
+      </c>
+      <c r="D77" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="78" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="B78" t="s">
+        <v>50</v>
+      </c>
+      <c r="C78">
+        <v>77.5</v>
+      </c>
+      <c r="D78">
+        <v>22.5</v>
+      </c>
+    </row>
+    <row r="79" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="B79" t="s">
+        <v>49</v>
+      </c>
+      <c r="C79">
+        <v>75.400000000000006</v>
+      </c>
+      <c r="D79">
+        <v>24.6</v>
+      </c>
+    </row>
+    <row r="80" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="B80" t="s">
+        <v>48</v>
+      </c>
+      <c r="C80">
+        <v>78.3</v>
+      </c>
+      <c r="D80">
+        <v>21.7</v>
+      </c>
+    </row>
+    <row r="81" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="B81" t="s">
+        <v>47</v>
+      </c>
+      <c r="C81">
+        <v>78</v>
+      </c>
+      <c r="D81">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="82" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="B82" t="s">
+        <v>46</v>
+      </c>
+      <c r="C82">
+        <v>81.900000000000006</v>
+      </c>
+      <c r="D82">
+        <v>18.100000000000001</v>
+      </c>
+    </row>
+    <row r="83" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="B83" t="s">
+        <v>45</v>
+      </c>
+      <c r="C83">
+        <v>78.8</v>
+      </c>
+      <c r="D83">
+        <v>21.2</v>
+      </c>
+    </row>
+    <row r="84" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="B84" t="s">
+        <v>44</v>
+      </c>
+      <c r="C84">
+        <v>80.8</v>
+      </c>
+      <c r="D84">
+        <v>19.2</v>
+      </c>
+    </row>
+    <row r="89" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A89" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="90" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="B90" t="s">
+        <v>55</v>
+      </c>
+      <c r="C90">
+        <v>24.5</v>
+      </c>
+    </row>
+    <row r="91" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="B91" t="s">
+        <v>56</v>
+      </c>
+      <c r="C91">
+        <v>17.7</v>
+      </c>
+    </row>
+    <row r="92" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="B92" t="s">
+        <v>57</v>
+      </c>
+      <c r="C92">
+        <v>16.600000000000001</v>
+      </c>
+    </row>
+    <row r="93" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="B93" t="s">
+        <v>58</v>
+      </c>
+      <c r="C93">
+        <v>14.1</v>
+      </c>
+    </row>
+    <row r="94" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="B94" t="s">
+        <v>59</v>
+      </c>
+      <c r="C94">
+        <v>8.4</v>
+      </c>
+    </row>
+    <row r="95" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="B95" t="s">
+        <v>60</v>
+      </c>
+      <c r="C95">
+        <v>7.2</v>
+      </c>
+    </row>
+    <row r="96" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="B96" t="s">
+        <v>61</v>
+      </c>
+      <c r="C96">
+        <v>3.6</v>
+      </c>
+    </row>
+    <row r="97" spans="2:11" x14ac:dyDescent="0.45">
+      <c r="B97" t="s">
+        <v>62</v>
+      </c>
+      <c r="C97">
+        <v>2.2999999999999998</v>
+      </c>
+    </row>
+    <row r="98" spans="2:11" x14ac:dyDescent="0.45">
+      <c r="B98" t="s">
+        <v>6</v>
+      </c>
+      <c r="C98">
+        <v>5.7</v>
+      </c>
+    </row>
+    <row r="100" spans="2:11" x14ac:dyDescent="0.45">
+      <c r="C100" t="s">
+        <v>55</v>
+      </c>
+      <c r="D100" t="s">
+        <v>56</v>
+      </c>
+      <c r="E100" t="s">
+        <v>57</v>
+      </c>
+      <c r="F100" t="s">
+        <v>58</v>
+      </c>
+      <c r="G100" t="s">
+        <v>59</v>
+      </c>
+      <c r="H100" t="s">
+        <v>60</v>
+      </c>
+      <c r="I100" t="s">
+        <v>61</v>
+      </c>
+      <c r="J100" t="s">
+        <v>62</v>
+      </c>
+      <c r="K100" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="101" spans="2:11" x14ac:dyDescent="0.45">
+      <c r="C101">
+        <v>24.5</v>
+      </c>
+      <c r="D101">
+        <v>17.7</v>
+      </c>
+      <c r="E101">
+        <v>16.600000000000001</v>
+      </c>
+      <c r="F101">
+        <v>14.1</v>
+      </c>
+      <c r="G101">
+        <v>8.4</v>
+      </c>
+      <c r="H101">
+        <v>7.2</v>
+      </c>
+      <c r="I101">
+        <v>3.6</v>
+      </c>
+      <c r="J101">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="K101">
+        <v>5.7</v>
       </c>
     </row>
   </sheetData>
